--- a/human_resources_forms/032_employee_competency_mapping_evaluation_form--human_resources_forms.xlsx
+++ b/human_resources_forms/032_employee_competency_mapping_evaluation_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'human_resources'}</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Human Resources'}</t>
+          <t>Human Resources</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'semi-annually'}</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Semi-Annually'}</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'on_leave'}</t>
+          <t>on_leave</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'On Leave'}</t>
+          <t>On Leave</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'mastery'}</t>
+          <t>mastery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Mastery'}</t>
+          <t>Mastery</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'required'}</t>
+          <t>required</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Required'}</t>
+          <t>Required</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'nice_to_have'}</t>
+          <t>nice_to_have</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Nice to Have'}</t>
+          <t>Nice to Have</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_required'}</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Required'}</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
